--- a/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
+++ b/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -16629,7 +16629,7 @@
           <t>A | 2115呎 (开放式)
 $13680万
 $64,681/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -16645,7 +16645,7 @@
           <t>A | 1438呎 (4+房)
 $7026万
 $48,860/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -16653,7 +16653,7 @@
           <t>B | 1117呎 (3房)
 $5013万
 $44,879/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
           <t>A | 1438呎 (4+房)
 $6411万
 $44,582/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -16676,7 +16676,7 @@
           <t>B | 1117呎 (3房)
 $4680万
 $41,898/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -16691,7 +16691,7 @@
           <t>A | 1438呎 (4+房)
 $6277万
 $43,653/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -16699,7 +16699,7 @@
           <t>B | 1117呎 (3房)
 $4642万
 $41,558/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -16714,7 +16714,7 @@
           <t>A | 1438呎 (4+房)
 $6129万
 $42,622/呎
-(24年-12月-04日)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -16722,7 +16722,7 @@
           <t>B | 1117呎 (3房)
 $4598万
 $41,162/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
           <t>A | 1438呎 (4+房)
 $6731万
 $46,809/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -16745,7 +16745,7 @@
           <t>B | 1117呎 (3房)
 $4538万
 $40,627/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
           <t>A | 1438呎 (4+房)
 $6637万
 $46,156/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -16768,7 +16768,7 @@
           <t>B | 1117呎 (3房)
 $4397万
 $39,363/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
           <t>A | 1438呎 (4+房)
 $6159万
 $42,828/呎
-(25年-04月-21日)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -16791,7 +16791,7 @@
           <t>B | 1117呎 (3房)
 $4436万
 $39,715/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
           <t>A | 1438呎 (4+房)
 $5610万
 $39,009/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -16814,7 +16814,7 @@
           <t>B | 1117呎 (3房)
 $4537万
 $40,618/呎
-(24年-12月-29日)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16829,7 @@
           <t>A | 1438呎 (4+房)
 $5438万
 $37,816/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -16837,7 +16837,7 @@
           <t>B | 1117呎 (3房)
 $4220万
 $37,780/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
           <t>A | 1438呎 (4+房)
 $5600万
 $38,943/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -16860,7 +16860,7 @@
           <t>B | 1117呎 (3房)
 $3960万
 $35,452/呎
-(25年-03月-02日)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -16875,7 +16875,7 @@
           <t>A | 1438呎 (4+房)
 $5268万
 $36,636/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -16883,7 +16883,7 @@
           <t>B | 1117呎 (3房)
 $4016万
 $35,952/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
           <t>A | 1372呎 (4+房)
 $6806万
 $49,609/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -16906,7 +16906,7 @@
           <t>B | 1063呎 (3房)
 $4218万
 $39,680/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
           <t>A | 2058呎 (4+房)
 $12863万
 $62,504/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -17064,7 +17064,7 @@
           <t>A | 1437呎 (4+房)
 $6379万
 $44,388/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -17072,7 +17072,7 @@
           <t>B | 1107呎 (3房)
 $4850万
 $43,812/呎
-(25年-01月-12日)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -17087,7 +17087,7 @@
           <t>A | 1437呎 (4+房)
 $5902万
 $41,074/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -17095,7 +17095,7 @@
           <t>B | 1107呎 (3房)
 $4727万
 $42,704/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
           <t>A | 1437呎 (4+房)
 $6008万
 $41,809/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -17118,7 +17118,7 @@
           <t>B | 1107呎 (3房)
 $4645万
 $41,964/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
           <t>A | 1437呎 (4+房)
 $5739万
 $39,936/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -17141,7 +17141,7 @@
           <t>B | 1107呎 (3房)
 $4450万
 $40,199/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
           <t>A | 1437呎 (4+房)
 $5450万
 $37,926/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -17164,7 +17164,7 @@
           <t>B | 1107呎 (3房)
 $5001万
 $45,172/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17179,7 @@
           <t>A | 1437呎 (4+房)
 $5887万
 $40,967/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17187,7 +17187,7 @@
           <t>B | 1107呎 (3房)
 $4280万
 $38,663/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
           <t>A | 1437呎 (4+房)
 $5454万
 $37,957/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -17210,7 +17210,7 @@
           <t>B | 1107呎 (3房)
 $4119万
 $37,207/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
           <t>A | 1483呎 (4+房)
 $5420万
 $36,548/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -17233,7 +17233,7 @@
           <t>B | 1107呎 (3房)
 $4214万
 $38,067/呎
-(24年-12月-01日)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17248,7 @@
           <t>A | 1437呎 (4+房)
 $5372万
 $37,385/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -17256,7 +17256,7 @@
           <t>B | 1107呎 (3房)
 $4100万
 $37,037/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17271,7 @@
           <t>A | 1437呎 (4+房)
 $5468万
 $38,051/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -17279,7 +17279,7 @@
           <t>B | 1107呎 (3房)
 $4087万
 $36,918/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
           <t>A | 1437呎 (4+房)
 $4968万
 $34,572/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -17302,7 +17302,7 @@
           <t>B | 1107呎 (3房)
 $3920万
 $35,411/呎
-(24年-10月-20日)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -17317,7 +17317,7 @@
           <t>A | 1437呎 (4+房)
 $5116万
 $35,604/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -17325,7 +17325,7 @@
           <t>B | 1153呎 (3房)
 $3984万
 $34,550/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17340,7 @@
           <t>A | 1437呎 (4+房)
 $5478万
 $38,120/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -17348,7 +17348,7 @@
           <t>B | 1090呎 (3房)
 $4289万
 $39,348/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="L5" s="20" t="inlineStr">
         <is>
-          <t>L | 373呎 (1房)
+          <t>L | 372呎 (1房)
 -
 -
 (待售)</t>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>F | 387呎 (1房)
+          <t>F | 386呎 (1房)
 -
 -
 (待售)</t>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>F | 387呎 (1房)
+          <t>F | 386呎 (1房)
 -
 -
 (待售)</t>
@@ -18092,7 +18092,7 @@
           <t>B | 509呎 (2房)
 $6827万
 $134,126/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">

--- a/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
+++ b/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 670呎 (3房)
+          <t>A | 671呎 (3房)
 -
 -
 (待售)</t>

--- a/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
+++ b/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>L | 373呎 (1房)
+          <t>L | 372呎 (1房)
 -
 -
 (待售)</t>

--- a/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
+++ b/港岛-北角-海璇 II (第2B-3期)/海璇 II (第2B-3期)_销控明细表.xlsx
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>H | 361呎 (1房)
+          <t>H | 358呎 (1房)
 -
 -
 (待售)</t>
@@ -17971,7 +17971,7 @@
       </c>
       <c r="L9" s="20" t="inlineStr">
         <is>
-          <t>L | 373呎 (1房)
+          <t>L | 372呎 (1房)
 -
 -
 (待售)</t>
